--- a/docs/listening-pingpong-template.xlsx
+++ b/docs/listening-pingpong-template.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>밑줄 칠 실제 단어(예: towels). 점선 밑줄 자동. (선택)</t>
+          <t>밑줄 칠 실제 단어(예: latte). 점선 밑줄 자동. (선택)</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>예시(Where's ~?)</t>
+          <t>예시(I'll have ~.)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Welcome! ... Do you need directions?  (예/아니오 질문)</t>
+          <t>Hi! Are you ready to order?  (예/아니오 질문)</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Yes, where's the elevator?  (Yes + 배운 표현)</t>
+          <t>Yes, I'll have a latte.  (Yes + 배운 표현)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>I'll have the elevator.  (표현 오용)</t>
+          <t>Where's the latte?  (주문 전 위치 — 표현 오용)</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>No, it's on the roof!  (엉뚱)</t>
+          <t>Can I get a dinosaur?  (엉뚱)</t>
         </is>
       </c>
     </row>
@@ -1034,40 +1034,40 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>elevator</t>
+          <t>latte</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>엘리베이터</t>
+          <t>카페 라떼</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>2557</v>
+        <v>5835</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0002557.K0wWy.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0005835.LIXaP.ogg</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Where's the elevator?</t>
+          <t>I'll have a latte.</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>엘리베이터는 어디에 있나요?</t>
+          <t>라떼로 주세요.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>호텔 로비</t>
+          <t>카페 주문</t>
         </is>
       </c>
     </row>
@@ -1077,20 +1077,20 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>latte</t>
+          <t>sandwich</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>카페 라떼</t>
+          <t>샌드위치</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>5835</v>
+        <v>2016</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0005835.LIXaP.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0002016.6j43f.ogg</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1100,17 +1100,17 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>I'll have a latte.</t>
+          <t>I'll have a sandwich.</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>라떼로 주세요.</t>
+          <t>샌드위치로 주세요.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>카페 주문</t>
+          <t>샌드위치 가게</t>
         </is>
       </c>
     </row>
@@ -1120,40 +1120,40 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>station</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>역 (기차)</t>
+          <t>샐러드</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3837</v>
+        <v>195</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0003837.FK9Se.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0000195.8PyYF.ogg</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>howget</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>How do I get to the station?</t>
+          <t>I'll have a salad.</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>역에 어떻게 가나요?</t>
+          <t>샐러드로 주세요.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>길 묻기</t>
+          <t>레스토랑</t>
         </is>
       </c>
     </row>
@@ -1163,40 +1163,40 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>charger</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>충전기</t>
+          <t>햄버거</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35848</v>
+        <v>36437</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0035848.77ZYw.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0036437.ZUAJp.ogg</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Do you have a charger?</t>
+          <t>I'll have a burger.</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>충전기가 있나요?</t>
+          <t>버거로 주세요.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>프런트 데스크</t>
+          <t>버거 가게</t>
         </is>
       </c>
     </row>
@@ -1206,40 +1206,40 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>towel</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>수건, 타월</t>
+          <t>케이크</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4107</v>
+        <v>1589</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0004107.xI4vn.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0001589.CONKy.ogg</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Can I get some towels?</t>
+          <t>I'll have some cake.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>수건 좀 받을 수 있을까요?</t>
+          <t>케이크로 주세요.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>룸서비스</t>
+          <t>베이커리</t>
         </is>
       </c>
     </row>
@@ -1249,40 +1249,40 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>umbrella</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>우산</t>
+          <t>차</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3272</v>
+        <v>3478</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0003272.gjTs2.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0003478.7o4ES.ogg</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>borrow</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Can I borrow an umbrella?</t>
+          <t>I'll have some tea.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>우산을 빌릴 수 있을까요?</t>
+          <t>차로 주세요.</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>친구에게 빌리기</t>
+          <t>티하우스</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Welcome! Your room's on the 15th floor. Do you need directions?</t>
+          <t>Hi! Are you ready to order?</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Yes, where's the elevator?</t>
+          <t>Yes, I'll have a latte.</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -1398,17 +1398,17 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>elevator</t>
+          <t>latte</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>‘길 안내가 필요하냐’는 물음에 ‘네, 엘리베이터는 어디예요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘주문하시겠어요?’에 ‘네, 라떼로 주세요’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -1426,19 +1426,23 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>I'll have the elevator.</t>
+          <t>Where's the latte?</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>latte</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>‘I'll have ~’는 주문 표현이에요. 엘리베이터는 주문할 수 없죠.</t>
+          <t>주문하는 자리에서 위치를 묻는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -1456,15 +1460,19 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>No, it's on the roof!</t>
+          <t>Can I get a dinosaur?</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>엘리베이터가 옥상에 있다니, 엉뚱한 답이에요.</t>
+          <t>공룡이라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1490,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Sure — it's around the corner. Can I help with your bags?</t>
+          <t>Sure. Would you like anything to eat?</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1504,7 +1512,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get a cart?</t>
+          <t>Yes, do you have any bagels?</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1514,13 +1522,13 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>‘짐 도와줄까요?’에 ‘네, 카트 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘드실 것 있으세요?’에 ‘네, 베이글 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -1538,19 +1546,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Where's my bag?</t>
+          <t>I'll have a table.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>가방은 본인이 들고 있는데 위치를 묻는 건 이상해요.</t>
+          <t>테이블을 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -1568,19 +1576,15 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>I'll have a helicopter.</t>
+          <t>At 3 o'clock.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>ill</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>헬리콥터라니, 엉뚱한 답이에요.</t>
+          <t>먹을 것을 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1602,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Of course. Are you interested in our facilities?</t>
+          <t>Great. Is this order to go?</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -1620,7 +1624,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have a gym?</t>
+          <t>Yes, can I get a to-go bag?</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1630,13 +1634,13 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>‘부대시설에 관심 있냐’는 물음에 ‘네, 헬스장 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘포장이세요?’에 ‘네, 포장 봉투 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -1654,19 +1658,23 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>I'll have a swimming pool!</t>
+          <t>Where's my latte?</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>latte</t>
+        </is>
+      </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>수영장을 주문할 순 없죠(엉뚱).</t>
+          <t>아직 만드는 중인데 어디 있냐 묻는 건 성급해요.</t>
         </is>
       </c>
     </row>
@@ -1684,15 +1692,19 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>At 3 o'clock.</t>
+          <t>I'll have it yesterday!</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>ill</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>시설이 있냐고 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>어제 받을 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1722,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>We have a gym on the second floor. Enjoy your stay!</t>
+          <t>You got it — coming right up!</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -1742,7 +1754,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Hi! Are you ready to order?</t>
+          <t>Hi there! Have you decided?</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -1764,7 +1776,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Yes, I'll have a latte.</t>
+          <t>Yes, I'll have a sandwich.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1779,12 +1791,12 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>latte</t>
+          <t>sandwich</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>‘주문하시겠어요?’에 ‘네, 라떼로 주세요’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘정하셨어요?’에 ‘네, 샌드위치로 주세요’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1814,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Where's the latte?</t>
+          <t>Where's the sandwich?</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -1813,12 +1825,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>latte</t>
+          <t>sandwich</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>주문하는 자리에서 위치를 묻는 건 엉뚱해요.</t>
+          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1848,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Can I get a dinosaur?</t>
+          <t>Can I get a spaceship?</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -1848,7 +1860,7 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>공룡이라니, 엉뚱한 답이에요.</t>
+          <t>우주선이라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1878,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Sure. Would you like anything to eat?</t>
+          <t>Good choice. Do you want anything to drink?</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -1888,7 +1900,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have any bagels?</t>
+          <t>Yes, do you have lemonade?</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1904,7 +1916,7 @@
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>‘드실 것 있으세요?’에 ‘네, 베이글 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘마실 것 드릴까요?’에 ‘네, 레모네이드 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1934,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>I'll have a table.</t>
+          <t>I'll have a chair.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -1934,7 +1946,7 @@
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>테이블을 주문할 순 없죠(엉뚱).</t>
+          <t>의자를 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1964,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>At 3 o'clock.</t>
+          <t>At noon.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -1960,7 +1972,7 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>먹을 것을 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>마실 것을 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1990,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Great. Is this order to go?</t>
+          <t>We do. Is that everything?</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2000,7 +2012,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get a to-go bag?</t>
+          <t>Yes, can I get a napkin?</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2016,7 +2028,7 @@
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>‘포장이세요?’에 ‘네, 포장 봉투 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘그게 다예요?’에 ‘네, 냅킨 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2046,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Where's my latte?</t>
+          <t>Where's my sandwich?</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2045,7 +2057,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>latte</t>
+          <t>sandwich</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2068,7 +2080,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>I'll have it yesterday!</t>
+          <t>I'll have it last week!</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2080,7 +2092,7 @@
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>어제 받을 순 없죠(엉뚱).</t>
+          <t>지난주에 받을 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2110,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>You got it — coming right up!</t>
+          <t>Coming right up!</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2130,7 +2142,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>You look lost. Are you trying to find the station?</t>
+          <t>Good evening. Are you ready to order?</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2152,7 +2164,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Yes, how do I get to the station?</t>
+          <t>Yes, I'll have a salad.</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -2162,17 +2174,17 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>howget</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>station</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>‘역을 찾느냐’는 물음에 ‘네, 역에 어떻게 가요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘주문하시겠어요?’에 ‘네, 샐러드로 주세요’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2190,23 +2202,23 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>I'll have the station.</t>
+          <t>Where's the salad?</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>station</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>역을 주문할 순 없죠(엉뚱).</t>
+          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -2224,15 +2236,19 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>At 6 o'clock.</t>
+          <t>Can I get a dragon?</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>어디로 가냐가 아니라 시간으로 답하는 건 엉뚱해요.</t>
+          <t>용이라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2266,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>It's two blocks straight ahead. Would a map help?</t>
+          <t>Excellent. Would you like some soup, too?</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2272,7 +2288,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have a map?</t>
+          <t>Yes, do you have tomato soup?</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -2288,7 +2304,7 @@
       <c r="G35" s="6" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>‘지도가 도움이 될까요?’에 ‘네, 지도 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘수프도 드릴까요?’에 ‘네, 토마토 수프 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2306,19 +2322,19 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>How do I get a map?</t>
+          <t>I'll have a waiter.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>howget</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>‘How do I get ~?’는 장소로 가는 길을 묻는 표현이에요.</t>
+          <t>웨이터를 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2352,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Turn left into the sky?</t>
+          <t>At 8 o'clock.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2344,7 +2360,7 @@
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>하늘로 좌회전이라니, 엉뚱한 답이에요.</t>
+          <t>수프를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2378,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Here you go. Do you need to buy a ticket?</t>
+          <t>Of course. Anything to drink?</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2384,7 +2400,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Yes, where's the ticket machine?</t>
+          <t>Yes, can I get some water?</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2394,13 +2410,13 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>‘표 사야 하냐’는 물음에 ‘네, 매표기 어디 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘마실 것 드릴까요?’에 ‘네, 물 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2418,19 +2434,23 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>How do I get to the ticket?</t>
+          <t>Where's my salad?</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>howget</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>salad</t>
+        </is>
+      </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>표로 가는 길을 물을 순 없어요(엉뚱).</t>
+          <t>아직 만드는 중인데 어디 있냐 묻는 건 성급해요.</t>
         </is>
       </c>
     </row>
@@ -2448,19 +2468,19 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Can I get a helicopter?</t>
+          <t>I'll have it in 3025!</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>헬리콥터라니, 엉뚱한 답이에요.</t>
+          <t>먼 미래에 받겠다니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2498,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Right inside the entrance. Safe travels!</t>
+          <t>I'll bring it right out!</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2510,7 +2530,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Front desk. Is there something you need?</t>
+          <t>Hi! Can I take your order?</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2532,7 +2552,7 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have a charger?</t>
+          <t>Yes, I'll have a burger.</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2542,17 +2562,17 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>charger</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>‘필요한 게 있냐’는 물음에 ‘네, 충전기 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘주문받을까요?’에 ‘네, 버거로 주세요’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2570,23 +2590,23 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>I'll have a charger.</t>
+          <t>Where's the burger?</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>charger</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>‘I'll have ~’는 주문 표현이라 프런트 요청엔 어색해요.</t>
+          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2624,19 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Nice weather today!</t>
+          <t>Can I get a unicorn?</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>대화와 상관없는 엉뚱한 답이에요.</t>
+          <t>유니콘이라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2654,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>We do — I'll send one up. Would you like some ice, too?</t>
+          <t>Sure. Would you like fries with that?</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2652,7 +2676,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get some ice?</t>
+          <t>Yes, do you have onion rings?</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2662,13 +2686,13 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>‘얼음도 드릴까요?’에 ‘네, 얼음 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘감자튀김 드릴까요?’에 ‘네, 어니언링 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2686,23 +2710,19 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Where's my charger?</t>
+          <t>I'll have a parking lot.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>charger</t>
-        </is>
-      </c>
+          <t>ill</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>방금 보내준다고 했는데 벌써 어디 있냐 묻는 건 성급해요.</t>
+          <t>주차장을 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -2720,19 +2740,15 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>I'll have a penguin.</t>
+          <t>At midnight.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>ill</t>
-        </is>
-      </c>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>펭귄이라니, 엉뚱한 답이에요.</t>
+          <t>사이드를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2766,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Sure. Do you need an extra pillow?</t>
+          <t>We do. Anything else for you?</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2772,7 +2788,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have a spare?</t>
+          <t>Yes, can I get some ketchup?</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2782,13 +2798,13 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>‘베개 더 필요하냐’는 물음에 ‘네, 여분 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘더 필요하세요?’에 ‘네, 케첩 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2806,19 +2822,23 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>How do I get a pillow?</t>
+          <t>Where's my burger?</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>howget</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr"/>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>burger</t>
+        </is>
+      </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>‘How do I get ~?’는 길을 묻는 표현이에요.</t>
+          <t>아직 만드는 중인데 어디 있냐 묻는 건 성급해요.</t>
         </is>
       </c>
     </row>
@@ -2836,15 +2856,19 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>At midnight, please.</t>
+          <t>I'll have it yesterday!</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>ill</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>베개가 필요하냐고 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>어제 받을 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2886,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>I'll bring one right up — good night!</t>
+          <t>Order coming right up!</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2894,7 +2918,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Housekeeping. Did you call for something?</t>
+          <t>Hello! Do you know what you'd like?</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -2916,7 +2940,7 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get some towels?</t>
+          <t>Yes, I'll have some cake.</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2926,17 +2950,17 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>towels</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>‘뭔가 부르셨냐’는 물음에 ‘네, 수건 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘무엇으로 드릴까요?’에 ‘네, 케이크로 주세요’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2954,23 +2978,23 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>I'll have some towels.</t>
+          <t>Where's the cake?</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>towels</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>‘I'll have ~’는 음식 주문 표현이라 요청엔 어색해요.</t>
+          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3012,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Can I get a dragon?</t>
+          <t>Can I get a rainbow?</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3000,7 +3024,7 @@
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>용이라니, 엉뚱한 답이에요.</t>
+          <t>무지개라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3042,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Of course. Are you missing anything else?</t>
+          <t>Great. Would you like it in a box?</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3040,7 +3064,7 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have a hairdryer?</t>
+          <t>Yes, do you have a gift box?</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -3056,7 +3080,7 @@
       <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>‘더 없는 게 있냐’는 물음에 ‘네, 드라이어 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘상자에 담아드릴까요?’에 ‘네, 선물 상자 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3074,19 +3098,19 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Where's the hairdryer?</t>
+          <t>I'll have the oven.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>있는지부터 물어야 하는데 위치부터 묻는 건 성급해요.</t>
+          <t>오븐을 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -3104,19 +3128,15 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>I'll have ten pizzas!</t>
+          <t>At 5 p.m.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>ill</t>
-        </is>
-      </c>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>객실 요청과 상관없는 엉뚱한 답이에요.</t>
+          <t>상자를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3154,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>I'll bring one. Would you like some water?</t>
+          <t>Sure. Anything else?</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3156,7 +3176,7 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get a bottle?</t>
+          <t>Yes, can I get some candles?</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -3172,7 +3192,7 @@
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>‘물 드릴까요?’에 ‘네, 한 병 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘더 필요하세요?’에 ‘네, 초 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3190,23 +3210,23 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>How do I get towels?</t>
+          <t>Where's my cake?</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>howget</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>towels</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>‘How do I get ~?’는 길을 묻는 표현이에요.</t>
+          <t>아직 담는 중인데 어디 있냐 묻는 건 성급해요.</t>
         </is>
       </c>
     </row>
@@ -3224,15 +3244,19 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>At 3 a.m., please.</t>
+          <t>I'll have it last year!</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>ill</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>물 드릴까 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>작년에 받을 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3274,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>No problem — right up!</t>
+          <t>All set — enjoy!</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3282,7 +3306,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>It's really pouring out. Are you going out anyway?</t>
+          <t>Welcome! Shall I start your order?</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3304,7 +3328,7 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I borrow an umbrella?</t>
+          <t>Yes, I'll have some tea.</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3314,17 +3338,17 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>borrow</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>umbrella</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>‘그래도 나갈 거냐’는 물음에 ‘응, 우산 좀 빌릴 수 있어?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘주문 시작할까요?’에 ‘네, 차로 주세요’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3342,23 +3366,23 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Can I get an umbrella?</t>
+          <t>Where's the tea?</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>umbrella</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>사서 갖는 게 아니라 잠깐 빌리는 거라 ‘Can I borrow ~?’가 맞아요.</t>
+          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -3376,19 +3400,19 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>I'll have some sunshine!</t>
+          <t>Can I get a helicopter?</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>햇빛을 주문할 순 없죠(엉뚱).</t>
+          <t>헬리콥터라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3430,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Sure, it's by the door. Do you need anything else?</t>
+          <t>Of course. Would you like milk with it?</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -3428,7 +3452,7 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I borrow a bag?</t>
+          <t>Yes, do you have oat milk?</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -3438,13 +3462,13 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>borrow</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>‘더 필요하냐’는 물음에 ‘응, 가방도 빌릴 수 있어?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘우유 넣어드릴까요?’에 ‘네, 오트밀크 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3462,23 +3486,19 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Where's the umbrella?</t>
+          <t>I'll have a mountain.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>umbrella</t>
-        </is>
-      </c>
+          <t>ill</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>방금 문 옆이라고 알려줬어요.</t>
+          <t>산을 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -3496,19 +3516,15 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Can I borrow the moon?</t>
+          <t>At 7 o'clock.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>borrow</t>
-        </is>
-      </c>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>달을 빌린다니, 엉뚱한 답이에요.</t>
+          <t>우유를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3542,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Here. Oh, do you have your keys?</t>
+          <t>We do. Anything to eat?</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -3548,7 +3564,7 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Actually no — do you have a spare?</t>
+          <t>Yes, can I get a scone?</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3558,13 +3574,13 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>‘열쇠 있냐’는 물음에 ‘아니, 여분 있어?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘드실 것 있으세요?’에 ‘네, 스콘 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3582,19 +3598,23 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>I'll have your keys.</t>
+          <t>Where's my tea?</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr"/>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>‘I'll have ~’지만, 열쇠를 주문할 순 없죠.</t>
+          <t>아직 우려내는 중인데 어디 있냐 묻는 건 성급해요.</t>
         </is>
       </c>
     </row>
@@ -3612,15 +3632,19 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Keys are at 5 o'clock.</t>
+          <t>I'll have it in 1850!</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>ill</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>열쇠 있냐고 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>먼 과거에 받을 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3662,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Here's the spare — let's go!</t>
+          <t>Coming right up!</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>

--- a/docs/listening-pingpong-template.xlsx
+++ b/docs/listening-pingpong-template.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>예시 1개 = 어휘 1개 → 표현 1개(배열) → 대화 1개. 어휘·표현·배열문장·제목.</t>
+          <t>예시 1개 = 어휘 1개 → 표현 1개(배열) → 대화 1개. 목록 순서 = 예시 순서.</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>작성 원칙 (품질 핵심)</t>
+          <t>작성 원칙</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr"/>
@@ -706,7 +706,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>오답은 명백히 틀리게 2종류: (a) 배운 표현을 틀린 맥락에 쓴 것, (b) 유쾌·엉뚱하거나 카테고리 불일치(장소 물음에 시간 등).</t>
+          <t>오답은 명백히 틀리게: (a) 배운 표현을 틀린 맥락에, (b) 유쾌·엉뚱/카테고리 불일치(장소 물음에 시간 등).</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>'그럴듯하게 맞을 수도 있는' 오답 금지 — 정답이 안 도드라짐.</t>
+          <t>'그럴듯하게 맞을 수도 있는' 오답 금지.</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>리스닝의 콘텐츠 단어는 배열 문장과 달라도 됨(패턴 일반화). 같은 단어 3번 반복 금지.</t>
+          <t>리스닝 콘텐츠 단어는 배열 문장과 달라도 됨. 같은 단어 3번 반복 금지.</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>선택지는 짧고 초급 수준. 표현·어휘는 실제 뱅크 항목만(지어내지 않기).</t>
+          <t>선택지는 짧고 초급 수준. 표현·어휘는 실제 뱅크 항목만.</t>
         </is>
       </c>
     </row>
@@ -755,66 +755,6 @@
       <c r="B26" s="3" t="inlineStr">
         <is>
           <t>한 대화에 B 문제 3개 권장(첫 B 턴부터).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>예시(I'll have ~.)</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Hi! Are you ready to order?  (예/아니오 질문)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B 정답</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Yes, I'll have a latte.  (Yes + 배운 표현)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B 오답1</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Where's the latte?  (주문 전 위치 — 표현 오용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B 오답2</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Can I get a dinosaur?  (엉뚱)</t>
         </is>
       </c>
     </row>
@@ -1077,40 +1017,40 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>sandwich</t>
+          <t>station</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>샌드위치</t>
+          <t>역 (기차)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2016</v>
+        <v>3837</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0002016.6j43f.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0003837.FK9Se.ogg</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>howget</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>I'll have a sandwich.</t>
+          <t>How do I get to the station?</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>샌드위치로 주세요.</t>
+          <t>역에 어떻게 가나요?</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>샌드위치 가게</t>
+          <t>길 묻기</t>
         </is>
       </c>
     </row>
@@ -1120,40 +1060,40 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>charger</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>샐러드</t>
+          <t>충전기</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>195</v>
+        <v>35848</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0000195.8PyYF.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0035848.77ZYw.ogg</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>I'll have a salad.</t>
+          <t>Do you have a charger?</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>샐러드로 주세요.</t>
+          <t>충전기가 있나요?</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>레스토랑</t>
+          <t>프런트 데스크</t>
         </is>
       </c>
     </row>
@@ -1163,40 +1103,40 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>towel</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>햄버거</t>
+          <t>수건, 타월</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>36437</v>
+        <v>4107</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0036437.ZUAJp.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0004107.xI4vn.ogg</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>I'll have a burger.</t>
+          <t>Can I get some towels?</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>버거로 주세요.</t>
+          <t>수건 좀 받을 수 있을까요?</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>버거 가게</t>
+          <t>룸서비스</t>
         </is>
       </c>
     </row>
@@ -1206,40 +1146,40 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>umbrella</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>케이크</t>
+          <t>우산</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1589</v>
+        <v>3272</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0001589.CONKy.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0003272.gjTs2.ogg</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>borrow</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>I'll have some cake.</t>
+          <t>Can I borrow an umbrella?</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>케이크로 주세요.</t>
+          <t>우산을 빌릴 수 있을까요?</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>베이커리</t>
+          <t>친구에게 빌리기</t>
         </is>
       </c>
     </row>
@@ -1249,40 +1189,40 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>elevator</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>차</t>
+          <t>엘리베이터</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3478</v>
+        <v>2557</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0003478.7o4ES.ogg</t>
+          <t>https://speech.epop.ai/sentence/actor/usFemaleNormal/0002557.K0wWy.ogg</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>I'll have some tea.</t>
+          <t>Where's the elevator?</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>차로 주세요.</t>
+          <t>엘리베이터는 어디에 있나요?</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>티하우스</t>
+          <t>호텔 로비</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1694,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Hi there! Have you decided?</t>
+          <t>You look lost. Are you trying to find the station?</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -1776,7 +1716,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Yes, I'll have a sandwich.</t>
+          <t>Yes, how do I get to the station?</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1786,17 +1726,17 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>howget</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>sandwich</t>
+          <t>station</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>‘정하셨어요?’에 ‘네, 샌드위치로 주세요’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘역을 찾느냐’는 물음에 ‘네, 역에 어떻게 가요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -1814,23 +1754,23 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Where's the sandwich?</t>
+          <t>I'll have the station.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>sandwich</t>
+          <t>station</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
+          <t>역을 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -1848,19 +1788,15 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Can I get a spaceship?</t>
+          <t>At 6 o'clock.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>get</t>
-        </is>
-      </c>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>우주선이라니, 엉뚱한 답이에요.</t>
+          <t>어디로 가냐가 아니라 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1814,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Good choice. Do you want anything to drink?</t>
+          <t>It's two blocks straight ahead. Would a map help?</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -1900,7 +1836,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have lemonade?</t>
+          <t>Yes, do you have a map?</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1916,7 +1852,7 @@
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>‘마실 것 드릴까요?’에 ‘네, 레모네이드 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘지도가 도움이 될까요?’에 ‘네, 지도 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -1934,19 +1870,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>I'll have a chair.</t>
+          <t>How do I get a map?</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>howget</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>의자를 주문할 순 없죠(엉뚱).</t>
+          <t>‘How do I get ~?’는 장소로 가는 길을 묻는 표현이에요.</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1900,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>At noon.</t>
+          <t>Turn left into the sky?</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -1972,7 +1908,7 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>마실 것을 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>하늘로 좌회전이라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1926,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>We do. Is that everything?</t>
+          <t>Here you go. Do you need to buy a ticket?</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2012,7 +1948,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get a napkin?</t>
+          <t>Yes, where's the ticket machine?</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2022,13 +1958,13 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>‘그게 다예요?’에 ‘네, 냅킨 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘표 사야 하냐’는 물음에 ‘네, 매표기 어디 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2046,23 +1982,19 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Where's my sandwich?</t>
+          <t>How do I get to the ticket?</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>sandwich</t>
-        </is>
-      </c>
+          <t>howget</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>아직 만드는 중인데 어디 있냐 묻는 건 성급해요.</t>
+          <t>표로 가는 길을 물을 순 없어요(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -2080,19 +2012,19 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>I'll have it last week!</t>
+          <t>Can I get a helicopter?</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>지난주에 받을 순 없죠(엉뚱).</t>
+          <t>헬리콥터라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2042,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Coming right up!</t>
+          <t>Right inside the entrance. Safe travels!</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2142,7 +2074,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Good evening. Are you ready to order?</t>
+          <t>Front desk. Is there something you need?</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2164,7 +2096,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Yes, I'll have a salad.</t>
+          <t>Yes, do you have a charger?</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -2174,17 +2106,17 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>charger</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>‘주문하시겠어요?’에 ‘네, 샐러드로 주세요’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘필요한 게 있냐’는 물음에 ‘네, 충전기 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2202,23 +2134,23 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Where's the salad?</t>
+          <t>I'll have a charger.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>charger</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
+          <t>‘I'll have ~’는 주문 표현이라 프런트 요청엔 어색해요.</t>
         </is>
       </c>
     </row>
@@ -2236,19 +2168,15 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Can I get a dragon?</t>
+          <t>Nice weather today!</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>get</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>용이라니, 엉뚱한 답이에요.</t>
+          <t>대화와 상관없는 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2194,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Excellent. Would you like some soup, too?</t>
+          <t>We do — I'll send one up. Would you like some ice, too?</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2288,7 +2216,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have tomato soup?</t>
+          <t>Yes, can I get some ice?</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -2298,13 +2226,13 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>‘수프도 드릴까요?’에 ‘네, 토마토 수프 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘얼음도 드릴까요?’에 ‘네, 얼음 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2322,19 +2250,23 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>I'll have a waiter.</t>
+          <t>Where's my charger?</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr"/>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>charger</t>
+        </is>
+      </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>웨이터를 주문할 순 없죠(엉뚱).</t>
+          <t>방금 보내준다고 했는데 벌써 어디 있냐 묻는 건 성급해요.</t>
         </is>
       </c>
     </row>
@@ -2352,15 +2284,19 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>At 8 o'clock.</t>
+          <t>I'll have a penguin.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>ill</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>수프를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>펭귄이라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2314,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Of course. Anything to drink?</t>
+          <t>Sure. Do you need an extra pillow?</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2400,7 +2336,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get some water?</t>
+          <t>Yes, do you have a spare?</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2410,13 +2346,13 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>‘마실 것 드릴까요?’에 ‘네, 물 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘베개 더 필요하냐’는 물음에 ‘네, 여분 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2434,23 +2370,19 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Where's my salad?</t>
+          <t>How do I get a pillow?</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>salad</t>
-        </is>
-      </c>
+          <t>howget</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>아직 만드는 중인데 어디 있냐 묻는 건 성급해요.</t>
+          <t>‘How do I get ~?’는 길을 묻는 표현이에요.</t>
         </is>
       </c>
     </row>
@@ -2468,19 +2400,15 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>I'll have it in 3025!</t>
+          <t>At midnight, please.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>ill</t>
-        </is>
-      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>먼 미래에 받겠다니, 엉뚱한 답이에요.</t>
+          <t>베개가 필요하냐고 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2426,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>I'll bring it right out!</t>
+          <t>I'll bring one right up — good night!</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2530,7 +2458,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Hi! Can I take your order?</t>
+          <t>Housekeeping. Did you call for something?</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2552,7 +2480,7 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Yes, I'll have a burger.</t>
+          <t>Yes, can I get some towels?</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2562,17 +2490,17 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>towels</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>‘주문받을까요?’에 ‘네, 버거로 주세요’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘뭔가 부르셨냐’는 물음에 ‘네, 수건 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2590,23 +2518,23 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Where's the burger?</t>
+          <t>I'll have some towels.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>towels</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
+          <t>‘I'll have ~’는 음식 주문 표현이라 요청엔 어색해요.</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2552,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Can I get a unicorn?</t>
+          <t>Can I get a dragon?</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2636,7 +2564,7 @@
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>유니콘이라니, 엉뚱한 답이에요.</t>
+          <t>용이라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2582,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Sure. Would you like fries with that?</t>
+          <t>Of course. Are you missing anything else?</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2676,7 +2604,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have onion rings?</t>
+          <t>Yes, do you have a hairdryer?</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2692,7 +2620,7 @@
       <c r="G49" s="6" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>‘감자튀김 드릴까요?’에 ‘네, 어니언링 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘더 없는 게 있냐’는 물음에 ‘네, 드라이어 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2710,19 +2638,19 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>I'll have a parking lot.</t>
+          <t>Where's the hairdryer?</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>주차장을 주문할 순 없죠(엉뚱).</t>
+          <t>있는지부터 물어야 하는데 위치부터 묻는 건 성급해요.</t>
         </is>
       </c>
     </row>
@@ -2740,15 +2668,19 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>At midnight.</t>
+          <t>I'll have ten pizzas!</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>ill</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>사이드를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>객실 요청과 상관없는 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2698,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>We do. Anything else for you?</t>
+          <t>I'll bring one. Would you like some water?</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2788,7 +2720,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get some ketchup?</t>
+          <t>Yes, can I get a bottle?</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2804,7 +2736,7 @@
       <c r="G53" s="6" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>‘더 필요하세요?’에 ‘네, 케첩 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘물 드릴까요?’에 ‘네, 한 병 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2822,23 +2754,23 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Where's my burger?</t>
+          <t>How do I get towels?</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>howget</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>towels</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>아직 만드는 중인데 어디 있냐 묻는 건 성급해요.</t>
+          <t>‘How do I get ~?’는 길을 묻는 표현이에요.</t>
         </is>
       </c>
     </row>
@@ -2856,19 +2788,15 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>I'll have it yesterday!</t>
+          <t>At 3 a.m., please.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>ill</t>
-        </is>
-      </c>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>어제 받을 순 없죠(엉뚱).</t>
+          <t>물 드릴까 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2814,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Order coming right up!</t>
+          <t>No problem — right up!</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2918,7 +2846,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Hello! Do you know what you'd like?</t>
+          <t>It's really pouring out. Are you going out anyway?</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -2940,7 +2868,7 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Yes, I'll have some cake.</t>
+          <t>Yes, can I borrow an umbrella?</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2950,17 +2878,17 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>borrow</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>umbrella</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>‘무엇으로 드릴까요?’에 ‘네, 케이크로 주세요’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘그래도 나갈 거냐’는 물음에 ‘응, 우산 좀 빌릴 수 있어?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -2978,23 +2906,23 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Where's the cake?</t>
+          <t>Can I get an umbrella?</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>umbrella</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
+          <t>사서 갖는 게 아니라 잠깐 빌리는 거라 ‘Can I borrow ~?’가 맞아요.</t>
         </is>
       </c>
     </row>
@@ -3012,19 +2940,19 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Can I get a rainbow?</t>
+          <t>I'll have some sunshine!</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>무지개라니, 엉뚱한 답이에요.</t>
+          <t>햇빛을 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -3042,7 +2970,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Great. Would you like it in a box?</t>
+          <t>Sure, it's by the door. Do you need anything else?</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3064,7 +2992,7 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have a gift box?</t>
+          <t>Yes, can I borrow a bag?</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -3074,13 +3002,13 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>borrow</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>‘상자에 담아드릴까요?’에 ‘네, 선물 상자 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘더 필요하냐’는 물음에 ‘응, 가방도 빌릴 수 있어?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3098,19 +3026,23 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>I'll have the oven.</t>
+          <t>Where's the umbrella?</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr"/>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>umbrella</t>
+        </is>
+      </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>오븐을 주문할 순 없죠(엉뚱).</t>
+          <t>방금 문 옆이라고 알려줬어요.</t>
         </is>
       </c>
     </row>
@@ -3128,15 +3060,19 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>At 5 p.m.</t>
+          <t>Can I borrow the moon?</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>borrow</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>상자를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>달을 빌린다니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3090,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Sure. Anything else?</t>
+          <t>Here. Oh, do you have your keys?</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3176,7 +3112,7 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get some candles?</t>
+          <t>Actually no — do you have a spare?</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -3186,13 +3122,13 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>‘더 필요하세요?’에 ‘네, 초 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘열쇠 있냐’는 물음에 ‘아니, 여분 있어?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3210,23 +3146,19 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Where's my cake?</t>
+          <t>I'll have your keys.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>cake</t>
-        </is>
-      </c>
+          <t>ill</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>아직 담는 중인데 어디 있냐 묻는 건 성급해요.</t>
+          <t>‘I'll have ~’지만, 열쇠를 주문할 순 없죠.</t>
         </is>
       </c>
     </row>
@@ -3244,19 +3176,15 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>I'll have it last year!</t>
+          <t>Keys are at 5 o'clock.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>ill</t>
-        </is>
-      </c>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>작년에 받을 순 없죠(엉뚱).</t>
+          <t>열쇠 있냐고 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3202,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>All set — enjoy!</t>
+          <t>Here's the spare — let's go!</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3306,7 +3234,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Welcome! Shall I start your order?</t>
+          <t>Welcome! Your room's on the 15th floor. Do you need directions?</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -3328,7 +3256,7 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Yes, I'll have some tea.</t>
+          <t>Yes, where's the elevator?</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3338,17 +3266,17 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>elevator</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>‘주문 시작할까요?’에 ‘네, 차로 주세요’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘길 안내가 필요하냐’는 물음에 ‘네, 엘리베이터는 어디예요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3366,23 +3294,19 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Where's the tea?</t>
+          <t>I'll have the elevator.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
+          <t>ill</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>주문 전에 위치를 묻는 건 엉뚱해요.</t>
+          <t>‘I'll have ~’는 주문 표현이에요. 엘리베이터는 주문할 수 없죠.</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3324,15 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Can I get a helicopter?</t>
+          <t>No, it's on the roof!</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>get</t>
-        </is>
-      </c>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>헬리콥터라니, 엉뚱한 답이에요.</t>
+          <t>엘리베이터가 옥상에 있다니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3350,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Of course. Would you like milk with it?</t>
+          <t>Sure — it's around the corner. Can I help with your bags?</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -3452,7 +3372,7 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Yes, do you have oat milk?</t>
+          <t>Yes, can I get a cart?</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -3462,13 +3382,13 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>get</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>‘우유 넣어드릴까요?’에 ‘네, 오트밀크 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘짐 도와줄까요?’에 ‘네, 카트 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3486,19 +3406,19 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>I'll have a mountain.</t>
+          <t>Where's my bag?</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>where</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>산을 주문할 순 없죠(엉뚱).</t>
+          <t>가방은 본인이 들고 있는데 위치를 묻는 건 이상해요.</t>
         </is>
       </c>
     </row>
@@ -3516,15 +3436,19 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>At 7 o'clock.</t>
+          <t>I'll have a helicopter.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>ill</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>우유를 물었는데 시간으로 답하는 건 엉뚱해요.</t>
+          <t>헬리콥터라니, 엉뚱한 답이에요.</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3466,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>We do. Anything to eat?</t>
+          <t>Of course. Are you interested in our facilities?</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -3564,7 +3488,7 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Yes, can I get a scone?</t>
+          <t>Yes, do you have a gym?</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3574,13 +3498,13 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>‘드실 것 있으세요?’에 ‘네, 스콘 받을 수 있어요?’로 답한 자연스러운 흐름이에요.</t>
+          <t>‘부대시설에 관심 있냐’는 물음에 ‘네, 헬스장 있어요?’로 답한 자연스러운 흐름이에요.</t>
         </is>
       </c>
     </row>
@@ -3598,23 +3522,19 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Where's my tea?</t>
+          <t>I'll have a swimming pool!</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
+          <t>ill</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>아직 우려내는 중인데 어디 있냐 묻는 건 성급해요.</t>
+          <t>수영장을 주문할 순 없죠(엉뚱).</t>
         </is>
       </c>
     </row>
@@ -3632,19 +3552,15 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>I'll have it in 1850!</t>
+          <t>At 3 o'clock.</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>ill</t>
-        </is>
-      </c>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>먼 과거에 받을 순 없죠(엉뚱).</t>
+          <t>시설이 있냐고 물었는데 시간으로 답하는 건 엉뚱해요.</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3578,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Coming right up!</t>
+          <t>We have a gym on the second floor. Enjoy your stay!</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
